--- a/個人成長體系/01_成長管理中心/個人成長管理中心_2026_V1.0.xlsx
+++ b/個人成長體系/01_成長管理中心/個人成長管理中心_2026_V1.0.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首頁" sheetId="1" r:id="Ra0863d3c0d0848b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成長戰略" sheetId="2" r:id="R770cc876994a4d1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="能力盤點" sheetId="3" r:id="Rc60f7c85da684805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證據紀錄" sheetId="4" r:id="Rb02b57a812a941e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="專案組合" sheetId="5" r:id="R1636e75fa5774192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12週計畫" sheetId="6" r:id="Rc886545b1842481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每週執行" sheetId="7" r:id="Rf43c0380c3fb489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月季檢討" sheetId="8" r:id="Raa9c469398ee4a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="9" r:id="R89bc890dd459428a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="10" r:id="R4d0ddc10932d4872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首頁" sheetId="1" r:id="R500a62048bcd4158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成長戰略" sheetId="2" r:id="R2f949e84f2574169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="能力盤點" sheetId="3" r:id="R014fbd1984e44dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證據紀錄" sheetId="4" r:id="Rf586e6b6d7624cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="專案組合" sheetId="5" r:id="Reeecb7299baf43f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12週計畫" sheetId="6" r:id="Rbe7b9eb649624528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每週執行" sheetId="7" r:id="R42a598c0fe8841f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月季檢討" sheetId="8" r:id="R59f32477ed7248fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="9" r:id="R2b686840eefb489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="10" r:id="R007c8168fd284e87"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -191,7 +191,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="107">
+  <x:cellXfs count="110">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -305,6 +305,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -782,7 +791,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4332ba3af457428a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4436a6bdc7d426e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -812,7 +821,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ebf393a978047b9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44d9a0f55c45434f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1526,7 +1535,7 @@
         <x:v>三年定位</x:v>
       </x:c>
       <x:c r="B4" s="30" t="str">
-        <x:v>成為能運用 AI、資料與流程方法，協助企業診斷 ERP 營運問題、設計改善方案並推動落地的智慧流程顧問。</x:v>
+        <x:v>資深 ERP 顧問＋流程／制度顧問＋AI／自動化顧問；採分階段疊加，不同時全面展開。</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>評選問題</x:v>
@@ -1545,7 +1554,7 @@
         <x:v>定位狀態</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>待本人確認；第一次季度考核校準</x:v>
+        <x:v>本人已提出方向；第一期季度考核依實戰證據校準</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>是否支援三年定位？</x:v>
@@ -1560,7 +1569,7 @@
         <x:v>本年度主題</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
-        <x:v>建立可重複的顧問工作方法與個人成長作業系統</x:v>
+        <x:v>建立系統導入顧問基本功：Odoo進銷存、商業流程、八大循環、訪談與專案跟進</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>六個月內有使用場景？</x:v>
@@ -1575,7 +1584,7 @@
         <x:v>年度核心成果</x:v>
       </x:c>
       <x:c r="B7" s="31" t="str">
-        <x:v>完成4個12週循環；形成至少4項可重用資產</x:v>
+        <x:v>完成至少2個12週循環；形成新手顧問導入基礎包與一項可獨立處理的流程能力</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>能形成成果或證據？</x:v>
@@ -1590,7 +1599,7 @@
         <x:v>優先服務問題</x:v>
       </x:c>
       <x:c r="B8" s="31" t="str">
-        <x:v>待盤點</x:v>
+        <x:v>新手如何把Odoo功能、商業進銷存、八大循環與真實專案串起來</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>能與ERP經驗結合？</x:v>
@@ -1605,7 +1614,7 @@
         <x:v>主要領域／流程</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>待盤點</x:v>
+        <x:v>Odoo銷售、採購、庫存；建大復盤與興宇貿易導入</x:v>
       </x:c>
       <x:c r="D9" s="22" t="str">
         <x:v>AI進步後仍有互補價值？</x:v>
@@ -1620,7 +1629,7 @@
         <x:v>希望增加的工作</x:v>
       </x:c>
       <x:c r="B10" s="31" t="str">
-        <x:v>診斷、查證、整合、協調、落地</x:v>
+        <x:v>流程理解、需求訪談、專案跟進、實際操作、案例復盤</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1628,7 +1637,7 @@
         <x:v>希望降低的工作</x:v>
       </x:c>
       <x:c r="B11" s="31" t="str">
-        <x:v>重複整理、制式產出、無目的工具學習</x:v>
+        <x:v>無目的全面學習、只看課不操作、晚間長期高負荷學習</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1636,7 +1645,7 @@
         <x:v>每週可投入時間</x:v>
       </x:c>
       <x:c r="B12" s="31" t="str">
-        <x:v>待填寫</x:v>
+        <x:v>主要使用上班學習時段；暫估10–15小時，兩週後校準；晚上不強制</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1644,7 +1653,7 @@
         <x:v>外部回饋者</x:v>
       </x:c>
       <x:c r="B13" s="31" t="str">
-        <x:v>待指定</x:v>
+        <x:v>待指定主管、資深顧問或專案同事</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1652,7 +1661,7 @@
         <x:v>年度限制條件</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
-        <x:v>工作負荷、時間、資料機密及身心狀態</x:v>
+        <x:v>工作與生活平衡、動力維持、專案時程與資料機密</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1783,7 +1792,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J4" s="30" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1813,7 +1822,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J5" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1843,7 +1852,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J6" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1873,7 +1882,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J7" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1903,7 +1912,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J8" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1933,7 +1942,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J9" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1963,7 +1972,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J10" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1971,29 +1980,32 @@
         <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B11" s="28" t="str">
-        <x:v>跨模組流程理解</x:v>
+        <x:v>Odoo核心模組操作</x:v>
       </x:c>
       <x:c r="C11" s="34" t="str">
-        <x:v>理解訂單、採購、庫存、財會等資料連動</x:v>
-      </x:c>
-      <x:c r="D11" s="37"/>
+        <x:v>能在測試環境完成銷售、採購、庫存端到端流程</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E11" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F11" s="28" t="str">
+      <x:c r="F11" s="28" t="n">
         <x:f>IF(OR(D11="",E11=""),"",E11-D11)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G11" s="28" t="str">
-        <x:v>E0</x:v>
+        <x:v>E1</x:v>
       </x:c>
       <x:c r="H11" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I11" s="28" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J11" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>新手學習中；已有部分專案接觸，待操作證據校準</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2001,12 +2013,14 @@
         <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B12" s="28" t="str">
-        <x:v>主資料治理</x:v>
+        <x:v>商業進銷存基礎</x:v>
       </x:c>
       <x:c r="C12" s="34" t="str">
-        <x:v>辨識編碼、責任、品質與變更控制</x:v>
-      </x:c>
-      <x:c r="D12" s="37"/>
+        <x:v>理解單據、狀態、主資料、物流與帳務的基本關係</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E12" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -2017,13 +2031,13 @@
         <x:v>E0</x:v>
       </x:c>
       <x:c r="H12" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I12" s="28" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J12" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>本人明確表示為主要痛點</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2031,14 +2045,16 @@
         <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B13" s="28" t="str">
-        <x:v>內控與權責</x:v>
+        <x:v>八大循環與內控基礎</x:v>
       </x:c>
       <x:c r="C13" s="34" t="str">
-        <x:v>設計授權、核准、勾稽、追溯及例外</x:v>
-      </x:c>
-      <x:c r="D13" s="37"/>
+        <x:v>理解各循環目的、風險、控制點及與系統的連結</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E13" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="28" t="str">
         <x:f>IF(OR(D13="",E13=""),"",E13-D13)</x:f>
@@ -2047,13 +2063,13 @@
         <x:v>E0</x:v>
       </x:c>
       <x:c r="H13" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I13" s="28" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="J13" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>第一期先建立定位圖，不要求深入精通</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2061,14 +2077,16 @@
         <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B14" s="28" t="str">
-        <x:v>流程異常診斷</x:v>
+        <x:v>跨模組流程理解</x:v>
       </x:c>
       <x:c r="C14" s="34" t="str">
-        <x:v>區分系統、資料、流程及人的原因</x:v>
-      </x:c>
-      <x:c r="D14" s="37"/>
+        <x:v>理解訂單、採購、庫存、財會等資料連動</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E14" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="28" t="str">
         <x:f>IF(OR(D14="",E14=""),"",E14-D14)</x:f>
@@ -2077,13 +2095,13 @@
         <x:v>E0</x:v>
       </x:c>
       <x:c r="H14" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I14" s="28" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="J14" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>隨進銷存實作逐步建立</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2091,10 +2109,10 @@
         <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B15" s="28" t="str">
-        <x:v>產業情境理解</x:v>
+        <x:v>主資料治理</x:v>
       </x:c>
       <x:c r="C15" s="34" t="str">
-        <x:v>將標準流程調整為可落地產業作法</x:v>
+        <x:v>辨識編碼、責任、品質與變更控制</x:v>
       </x:c>
       <x:c r="D15" s="37"/>
       <x:c r="E15" s="41" t="n">
@@ -2113,18 +2131,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J15" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="20" t="str">
-        <x:v>資料與AI</x:v>
+        <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B16" s="28" t="str">
-        <x:v>Excel與資料整理</x:v>
+        <x:v>內控與權責</x:v>
       </x:c>
       <x:c r="C16" s="34" t="str">
-        <x:v>可重現地清理、比對及彙總資料</x:v>
+        <x:v>設計授權、核准、勾稽、追溯及例外</x:v>
       </x:c>
       <x:c r="D16" s="37"/>
       <x:c r="E16" s="41" t="n">
@@ -2143,18 +2161,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J16" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="20" t="str">
-        <x:v>資料與AI</x:v>
+        <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
-        <x:v>SQL查詢</x:v>
+        <x:v>流程異常診斷</x:v>
       </x:c>
       <x:c r="C17" s="34" t="str">
-        <x:v>跨單據查核差異並解釋結果</x:v>
+        <x:v>區分系統、資料、流程及人的原因</x:v>
       </x:c>
       <x:c r="D17" s="37"/>
       <x:c r="E17" s="41" t="n">
@@ -2173,18 +2191,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J17" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="20" t="str">
-        <x:v>資料與AI</x:v>
+        <x:v>ERP與流程</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>資料品質</x:v>
+        <x:v>產業情境理解</x:v>
       </x:c>
       <x:c r="C18" s="34" t="str">
-        <x:v>檢查完整性、一致性、正確性與時效</x:v>
+        <x:v>將標準流程調整為可落地產業作法</x:v>
       </x:c>
       <x:c r="D18" s="37"/>
       <x:c r="E18" s="41" t="n">
@@ -2203,7 +2221,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J18" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2211,20 +2229,23 @@
         <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
-        <x:v>API與整合概念</x:v>
+        <x:v>Excel與資料整理</x:v>
       </x:c>
       <x:c r="C19" s="34" t="str">
-        <x:v>理解事件、欄位、錯誤、重送與權限</x:v>
-      </x:c>
-      <x:c r="D19" s="37"/>
+        <x:v>可重現地清理、比對及彙總資料</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E19" s="41" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F19" s="28" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F19" s="28" t="n">
         <x:f>IF(OR(D19="",E19=""),"",E19-D19)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="28" t="str">
-        <x:v>E0</x:v>
+        <x:v>E1</x:v>
       </x:c>
       <x:c r="H19" s="28" t="str">
         <x:v>低</x:v>
@@ -2233,7 +2254,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J19" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>本人表示已有使用能力，程度待實作校準</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2241,10 +2262,10 @@
         <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B20" s="28" t="str">
-        <x:v>AI協作設計</x:v>
+        <x:v>SQL查詢</x:v>
       </x:c>
       <x:c r="C20" s="34" t="str">
-        <x:v>定義輸入、上下文、工具及人工判斷點</x:v>
+        <x:v>跨單據查核差異並解釋結果</x:v>
       </x:c>
       <x:c r="D20" s="37"/>
       <x:c r="E20" s="41" t="n">
@@ -2263,7 +2284,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J20" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2271,10 +2292,10 @@
         <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
-        <x:v>AI評測與驗證</x:v>
+        <x:v>資料品質</x:v>
       </x:c>
       <x:c r="C21" s="34" t="str">
-        <x:v>建立測試案例、門檻、抽查及復原方式</x:v>
+        <x:v>檢查完整性、一致性、正確性與時效</x:v>
       </x:c>
       <x:c r="D21" s="37"/>
       <x:c r="E21" s="41" t="n">
@@ -2293,7 +2314,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J21" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2301,10 +2322,10 @@
         <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B22" s="28" t="str">
-        <x:v>工作流自動化</x:v>
+        <x:v>API與整合概念</x:v>
       </x:c>
       <x:c r="C22" s="34" t="str">
-        <x:v>將重複任務改為可監控、可維護流程</x:v>
+        <x:v>理解事件、欄位、錯誤、重送與權限</x:v>
       </x:c>
       <x:c r="D22" s="37"/>
       <x:c r="E22" s="41" t="n">
@@ -2323,28 +2344,31 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J22" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="20" t="str">
-        <x:v>顧問能力</x:v>
+        <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
-        <x:v>訪談與提問</x:v>
+        <x:v>AI協作設計</x:v>
       </x:c>
       <x:c r="C23" s="34" t="str">
-        <x:v>取得事實、例外、矛盾及利害關係</x:v>
-      </x:c>
-      <x:c r="D23" s="37"/>
+        <x:v>定義輸入、上下文、工具及人工判斷點</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E23" s="41" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F23" s="28" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F23" s="28" t="n">
         <x:f>IF(OR(D23="",E23=""),"",E23-D23)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="28" t="str">
-        <x:v>E0</x:v>
+        <x:v>E1</x:v>
       </x:c>
       <x:c r="H23" s="28" t="str">
         <x:v>低</x:v>
@@ -2353,18 +2377,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J23" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>本人表示已有AI工具能力，程度待實作校準</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="20" t="str">
-        <x:v>顧問能力</x:v>
+        <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B24" s="28" t="str">
-        <x:v>需求分析</x:v>
+        <x:v>AI評測與驗證</x:v>
       </x:c>
       <x:c r="C24" s="34" t="str">
-        <x:v>把需求轉成範圍、規則、驗收與限制</x:v>
+        <x:v>建立測試案例、門檻、抽查及復原方式</x:v>
       </x:c>
       <x:c r="D24" s="37"/>
       <x:c r="E24" s="41" t="n">
@@ -2383,18 +2407,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J24" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="20" t="str">
-        <x:v>顧問能力</x:v>
+        <x:v>資料與AI</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
-        <x:v>流程設計</x:v>
+        <x:v>工作流自動化</x:v>
       </x:c>
       <x:c r="C25" s="34" t="str">
-        <x:v>區分現行、建議、系統、權責及例外</x:v>
+        <x:v>將重複任務改為可監控、可維護流程</x:v>
       </x:c>
       <x:c r="D25" s="37"/>
       <x:c r="E25" s="41" t="n">
@@ -2413,7 +2437,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J25" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2421,14 +2445,16 @@
         <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B26" s="28" t="str">
-        <x:v>方案評估</x:v>
+        <x:v>訪談與提問</x:v>
       </x:c>
       <x:c r="C26" s="34" t="str">
-        <x:v>比較效益、成本、風險及副作用</x:v>
-      </x:c>
-      <x:c r="D26" s="37"/>
+        <x:v>取得事實、例外、矛盾及利害關係</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E26" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F26" s="28" t="str">
         <x:f>IF(OR(D26="",E26=""),"",E26-D26)</x:f>
@@ -2437,13 +2463,13 @@
         <x:v>E0</x:v>
       </x:c>
       <x:c r="H26" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I26" s="28" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J26" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>興宇貿易專案作為實戰情境</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2451,10 +2477,10 @@
         <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B27" s="28" t="str">
-        <x:v>測試與驗收</x:v>
+        <x:v>需求分析</x:v>
       </x:c>
       <x:c r="C27" s="34" t="str">
-        <x:v>建立案例並追蹤缺陷與通過條件</x:v>
+        <x:v>把需求轉成範圍、規則、驗收與限制</x:v>
       </x:c>
       <x:c r="D27" s="37"/>
       <x:c r="E27" s="41" t="n">
@@ -2473,7 +2499,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J27" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2481,10 +2507,10 @@
         <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B28" s="28" t="str">
-        <x:v>導入與變更管理</x:v>
+        <x:v>流程設計</x:v>
       </x:c>
       <x:c r="C28" s="34" t="str">
-        <x:v>讓使用者理解、採用並維持新作法</x:v>
+        <x:v>區分現行、建議、系統、權責及例外</x:v>
       </x:c>
       <x:c r="D28" s="37"/>
       <x:c r="E28" s="41" t="n">
@@ -2503,18 +2529,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J28" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="20" t="str">
-        <x:v>軟實力</x:v>
+        <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B29" s="28" t="str">
-        <x:v>傾聽與同理</x:v>
+        <x:v>方案評估</x:v>
       </x:c>
       <x:c r="C29" s="34" t="str">
-        <x:v>理解對方意圖、限制及未明說顧慮</x:v>
+        <x:v>比較效益、成本、風險及副作用</x:v>
       </x:c>
       <x:c r="D29" s="37"/>
       <x:c r="E29" s="41" t="n">
@@ -2533,18 +2559,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J29" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="20" t="str">
-        <x:v>軟實力</x:v>
+        <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:v>口頭表達</x:v>
+        <x:v>測試與驗收</x:v>
       </x:c>
       <x:c r="C30" s="34" t="str">
-        <x:v>依對象清楚說明結論、依據與行動</x:v>
+        <x:v>建立案例並追蹤缺陷與通過條件</x:v>
       </x:c>
       <x:c r="D30" s="37"/>
       <x:c r="E30" s="41" t="n">
@@ -2563,18 +2589,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J30" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="20" t="str">
-        <x:v>軟實力</x:v>
+        <x:v>顧問能力</x:v>
       </x:c>
       <x:c r="B31" s="28" t="str">
-        <x:v>書面表達</x:v>
+        <x:v>導入與變更管理</x:v>
       </x:c>
       <x:c r="C31" s="34" t="str">
-        <x:v>產出可執行、可追溯的正式文件</x:v>
+        <x:v>讓使用者理解、採用並維持新作法</x:v>
       </x:c>
       <x:c r="D31" s="37"/>
       <x:c r="E31" s="41" t="n">
@@ -2593,7 +2619,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J31" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2601,10 +2627,10 @@
         <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B32" s="28" t="str">
-        <x:v>說服與談判</x:v>
+        <x:v>傾聽與同理</x:v>
       </x:c>
       <x:c r="C32" s="34" t="str">
-        <x:v>在利益不同時形成可接受方案</x:v>
+        <x:v>理解對方意圖、限制及未明說顧慮</x:v>
       </x:c>
       <x:c r="D32" s="37"/>
       <x:c r="E32" s="41" t="n">
@@ -2623,7 +2649,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J32" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2631,10 +2657,10 @@
         <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B33" s="28" t="str">
-        <x:v>衝突處理</x:v>
+        <x:v>口頭表達</x:v>
       </x:c>
       <x:c r="C33" s="34" t="str">
-        <x:v>區分事實、立場與利益並促成決策</x:v>
+        <x:v>依對象清楚說明結論、依據與行動</x:v>
       </x:c>
       <x:c r="D33" s="37"/>
       <x:c r="E33" s="41" t="n">
@@ -2653,7 +2679,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J33" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2661,10 +2687,10 @@
         <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B34" s="28" t="str">
-        <x:v>跨部門協作</x:v>
+        <x:v>書面表達</x:v>
       </x:c>
       <x:c r="C34" s="34" t="str">
-        <x:v>管理依賴、承諾、資訊與責任</x:v>
+        <x:v>產出可執行、可追溯的正式文件</x:v>
       </x:c>
       <x:c r="D34" s="37"/>
       <x:c r="E34" s="41" t="n">
@@ -2683,7 +2709,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J34" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2691,10 +2717,10 @@
         <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
-        <x:v>建立信任</x:v>
+        <x:v>說服與談判</x:v>
       </x:c>
       <x:c r="C35" s="34" t="str">
-        <x:v>保持一致、透明、守密並對承諾負責</x:v>
+        <x:v>在利益不同時形成可接受方案</x:v>
       </x:c>
       <x:c r="D35" s="37"/>
       <x:c r="E35" s="41" t="n">
@@ -2713,18 +2739,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J35" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="20" t="str">
-        <x:v>執行與身心</x:v>
+        <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
-        <x:v>專注與時間配置</x:v>
+        <x:v>衝突處理</x:v>
       </x:c>
       <x:c r="C36" s="34" t="str">
-        <x:v>保護高價值工作時間並減少切換</x:v>
+        <x:v>區分事實、立場與利益並促成決策</x:v>
       </x:c>
       <x:c r="D36" s="37"/>
       <x:c r="E36" s="41" t="n">
@@ -2743,18 +2769,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J36" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="20" t="str">
-        <x:v>執行與身心</x:v>
+        <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B37" s="28" t="str">
-        <x:v>情緒與壓力調節</x:v>
+        <x:v>跨部門協作</x:v>
       </x:c>
       <x:c r="C37" s="34" t="str">
-        <x:v>在高壓下保持判斷並適時求助</x:v>
+        <x:v>管理依賴、承諾、資訊與責任</x:v>
       </x:c>
       <x:c r="D37" s="37"/>
       <x:c r="E37" s="41" t="n">
@@ -2773,18 +2799,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J37" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="20" t="str">
-        <x:v>執行與身心</x:v>
+        <x:v>軟實力</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
-        <x:v>韌性與復原</x:v>
+        <x:v>建立信任</x:v>
       </x:c>
       <x:c r="C38" s="34" t="str">
-        <x:v>從失敗恢復且調整方法</x:v>
+        <x:v>保持一致、透明、守密並對承諾負責</x:v>
       </x:c>
       <x:c r="D38" s="37"/>
       <x:c r="E38" s="41" t="n">
@@ -2803,7 +2829,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J38" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2811,10 +2837,10 @@
         <x:v>執行與身心</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
-        <x:v>持續學習</x:v>
+        <x:v>專注與時間配置</x:v>
       </x:c>
       <x:c r="C39" s="34" t="str">
-        <x:v>以真實問題驅動輸入、練習與反饋</x:v>
+        <x:v>保護高價值工作時間並減少切換</x:v>
       </x:c>
       <x:c r="D39" s="37"/>
       <x:c r="E39" s="41" t="n">
@@ -2833,18 +2859,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J39" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="20" t="str">
-        <x:v>職涯與市場</x:v>
+        <x:v>執行與身心</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
-        <x:v>作品與案例</x:v>
+        <x:v>情緒與壓力調節</x:v>
       </x:c>
       <x:c r="C40" s="34" t="str">
-        <x:v>以去識別化成果證明能力</x:v>
+        <x:v>在高壓下保持判斷並適時求助</x:v>
       </x:c>
       <x:c r="D40" s="37"/>
       <x:c r="E40" s="41" t="n">
@@ -2863,18 +2889,18 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J40" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="20" t="str">
-        <x:v>職涯與市場</x:v>
+        <x:v>執行與身心</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
-        <x:v>方法論資產</x:v>
+        <x:v>韌性與復原</x:v>
       </x:c>
       <x:c r="C41" s="34" t="str">
-        <x:v>將經驗形成可重用、可教導的方法</x:v>
+        <x:v>從失敗恢復且調整方法</x:v>
       </x:c>
       <x:c r="D41" s="37"/>
       <x:c r="E41" s="41" t="n">
@@ -2893,80 +2919,164 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="J41" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>待優勢測評與實戰盤點</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="20" t="str">
-        <x:v>職涯與市場</x:v>
+        <x:v>執行與身心</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
-        <x:v>專業關係網絡</x:v>
+        <x:v>持續學習</x:v>
       </x:c>
       <x:c r="C42" s="34" t="str">
-        <x:v>建立可交換知識、機會與回饋的關係</x:v>
-      </x:c>
-      <x:c r="D42" s="37"/>
+        <x:v>以真實問題驅動輸入、練習與反饋</x:v>
+      </x:c>
+      <x:c r="D42" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E42" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F42" s="28" t="str">
+      <x:c r="F42" s="28" t="n">
         <x:f>IF(OR(D42="",E42=""),"",E42-D42)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G42" s="28" t="str">
-        <x:v>E0</x:v>
+        <x:v>E1</x:v>
       </x:c>
       <x:c r="H42" s="28" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I42" s="28" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="J42" s="31" t="str">
-        <x:v>待本人盤點</x:v>
+        <x:v>作為執行機制持續觀察，不占用本季三項主動能力名額</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="22" t="str">
+      <x:c r="A43" s="20" t="str">
         <x:v>職涯與市場</x:v>
       </x:c>
-      <x:c r="B43" s="29" t="str">
+      <x:c r="B43" s="28" t="str">
+        <x:v>作品與案例</x:v>
+      </x:c>
+      <x:c r="C43" s="34" t="str">
+        <x:v>以去識別化成果證明能力</x:v>
+      </x:c>
+      <x:c r="D43" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F43" s="28" t="n">
+        <x:f>IF(OR(D43="",E43=""),"",E43-D43)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="28" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="H43" s="28" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I43" s="28" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="str">
+        <x:v>建大專案可作第一筆去識別化復盤</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="20" t="str">
+        <x:v>職涯與市場</x:v>
+      </x:c>
+      <x:c r="B44" s="28" t="str">
+        <x:v>方法論資產</x:v>
+      </x:c>
+      <x:c r="C44" s="34" t="str">
+        <x:v>將經驗形成可重用、可教導的方法</x:v>
+      </x:c>
+      <x:c r="D44" s="37"/>
+      <x:c r="E44" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F44" s="28" t="str">
+        <x:f>IF(OR(D44="",E44=""),"",E44-D44)</x:f>
+      </x:c>
+      <x:c r="G44" s="28" t="str">
+        <x:v>E0</x:v>
+      </x:c>
+      <x:c r="H44" s="28" t="str">
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="I44" s="28" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="str">
+        <x:v>待優勢測評與實戰盤點</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="20" t="str">
+        <x:v>職涯與市場</x:v>
+      </x:c>
+      <x:c r="B45" s="28" t="str">
+        <x:v>專業關係網絡</x:v>
+      </x:c>
+      <x:c r="C45" s="34" t="str">
+        <x:v>建立可交換知識、機會與回饋的關係</x:v>
+      </x:c>
+      <x:c r="D45" s="37"/>
+      <x:c r="E45" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F45" s="28" t="str">
+        <x:f>IF(OR(D45="",E45=""),"",E45-D45)</x:f>
+      </x:c>
+      <x:c r="G45" s="28" t="str">
+        <x:v>E0</x:v>
+      </x:c>
+      <x:c r="H45" s="28" t="str">
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="I45" s="28" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="str">
+        <x:v>待優勢測評與實戰盤點</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="22" t="str">
+        <x:v>職涯與市場</x:v>
+      </x:c>
+      <x:c r="B46" s="29" t="str">
         <x:v>職涯選擇權</x:v>
       </x:c>
-      <x:c r="C43" s="35" t="str">
+      <x:c r="C46" s="35" t="str">
         <x:v>降低對單一公司、工具或產品的依賴</x:v>
       </x:c>
-      <x:c r="D43" s="38"/>
-      <x:c r="E43" s="42" t="n">
+      <x:c r="D46" s="38"/>
+      <x:c r="E46" s="42" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F43" s="29" t="str">
-        <x:f>IF(OR(D43="",E43=""),"",E43-D43)</x:f>
-      </x:c>
-      <x:c r="G43" s="29" t="str">
+      <x:c r="F46" s="29" t="str">
+        <x:f>IF(OR(D46="",E46=""),"",E46-D46)</x:f>
+      </x:c>
+      <x:c r="G46" s="29" t="str">
         <x:v>E0</x:v>
       </x:c>
-      <x:c r="H43" s="29" t="str">
+      <x:c r="H46" s="29" t="str">
         <x:v>低</x:v>
       </x:c>
-      <x:c r="I43" s="29" t="str">
+      <x:c r="I46" s="29" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="J43" s="32" t="str">
-        <x:v>待本人盤點</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="D44" s="39"/>
-      <x:c r="E44" s="43"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="D45" s="39"/>
-      <x:c r="E45" s="43"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="D46" s="39"/>
-      <x:c r="E46" s="43"/>
+      <x:c r="J46" s="32" t="str">
+        <x:v>待優勢測評與實戰盤點</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="D47" s="39"/>
@@ -2989,17 +3099,17 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:dataValidations count="4">
-    <x:dataValidation type="whole" operator="between" sqref="D4:E43">
+    <x:dataValidation type="whole" operator="between" sqref="D4:E46">
       <x:formula1>0</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="G4:G43">
+    <x:dataValidation type="list" sqref="G4:G46">
       <x:formula1>"E0,E1,E2,E3,E4"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H4:H43">
+    <x:dataValidation type="list" sqref="H4:H46">
       <x:formula1>"低,中,高"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I4:I43">
+    <x:dataValidation type="list" sqref="I4:I46">
       <x:formula1>"是,否"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -3919,38 +4029,88 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="18"/>
-      <x:c r="B4" s="27"/>
-      <x:c r="C4" s="27"/>
-      <x:c r="D4" s="27"/>
-      <x:c r="E4" s="27"/>
-      <x:c r="F4" s="27"/>
-      <x:c r="G4" s="27"/>
-      <x:c r="H4" s="27"/>
-      <x:c r="I4" s="27"/>
-      <x:c r="J4" s="27"/>
-      <x:c r="K4" s="27" t="str">
+      <x:c r="A4" s="18" t="str">
+        <x:v>PG-001</x:v>
+      </x:c>
+      <x:c r="B4" s="27" t="str">
+        <x:v>新手顧問導入基礎包</x:v>
+      </x:c>
+      <x:c r="C4" s="27" t="str">
+        <x:v>複合型</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="str">
+        <x:v>Odoo／進銷存／訪談／專案跟進</x:v>
+      </x:c>
+      <x:c r="E4" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H4" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I4" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J4" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K4" s="27" t="n">
         <x:f>IF(COUNTA(E4:J4)=0,"",SUM(E4:J4))</x:f>
-      </x:c>
-      <x:c r="L4" s="27"/>
-      <x:c r="M4" s="19"/>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L4" s="27" t="str">
+        <x:v>本季執行</x:v>
+      </x:c>
+      <x:c r="M4" s="19" t="str">
+        <x:v>依12週計畫逐週完成，以興宇貿易作實戰主線</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="20"/>
-      <x:c r="B5" s="28"/>
-      <x:c r="C5" s="28"/>
-      <x:c r="D5" s="28"/>
-      <x:c r="E5" s="28"/>
-      <x:c r="F5" s="28"/>
-      <x:c r="G5" s="28"/>
-      <x:c r="H5" s="28"/>
-      <x:c r="I5" s="28"/>
-      <x:c r="J5" s="28"/>
-      <x:c r="K5" s="28" t="str">
+      <x:c r="A5" s="20" t="str">
+        <x:v>PG-002</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="str">
+        <x:v>建大專案去識別化復盤</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>資產型</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str">
+        <x:v>作品與案例／復盤能力</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I5" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J5" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="n">
         <x:f>IF(COUNTA(E5:J5)=0,"",SUM(E5:J5))</x:f>
-      </x:c>
-      <x:c r="L5" s="28"/>
-      <x:c r="M5" s="21"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L5" s="28" t="str">
+        <x:v>候選</x:v>
+      </x:c>
+      <x:c r="M5" s="21" t="str">
+        <x:v>第7週完成案例紀錄，敏感資料不得進Git</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="20"/>
@@ -4338,73 +4498,73 @@
       <x:c r="A4" s="18" t="str">
         <x:v>循環期間</x:v>
       </x:c>
-      <x:c r="B4" s="47" t="str">
-        <x:v>待填寫</x:v>
-      </x:c>
-      <x:c r="D4" s="58" t="str">
+      <x:c r="B4" s="50" t="str">
+        <x:v>2026-08-10 至 2026-11-01（依專案時程可順延）</x:v>
+      </x:c>
+      <x:c r="D4" s="61" t="str">
         <x:v>規則：12週只設定1項核心能力、1個實戰專案及1項資產成果。沒有實戰情境的學習不得成為核心項目。</x:v>
       </x:c>
-      <x:c r="E4" s="58"/>
-      <x:c r="F4" s="58"/>
-      <x:c r="G4" s="58"/>
-      <x:c r="H4" s="58"/>
-      <x:c r="I4" s="58"/>
-      <x:c r="J4" s="58"/>
+      <x:c r="E4" s="61"/>
+      <x:c r="F4" s="61"/>
+      <x:c r="G4" s="61"/>
+      <x:c r="H4" s="61"/>
+      <x:c r="I4" s="61"/>
+      <x:c r="J4" s="61"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="20" t="str">
         <x:v>核心成果</x:v>
       </x:c>
-      <x:c r="B5" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B5" s="51" t="str">
+        <x:v>形成新手顧問導入基礎包，並能在指導下參與興宇貿易的流程理解、訪談準備、跟進或需求整理</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="str">
         <x:v>核心能力</x:v>
       </x:c>
-      <x:c r="B6" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B6" s="51" t="str">
+        <x:v>Odoo核心進銷存流程理解與操作</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="20" t="str">
         <x:v>支援能力1</x:v>
       </x:c>
-      <x:c r="B7" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B7" s="51" t="str">
+        <x:v>需求訪談與提問</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="str">
         <x:v>支援能力2</x:v>
       </x:c>
-      <x:c r="B8" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B8" s="51" t="str">
+        <x:v>專案跟進與知識沉澱</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="20" t="str">
         <x:v>實戰專案</x:v>
       </x:c>
-      <x:c r="B9" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B9" s="51" t="str">
+        <x:v>建大專案復盤＋興宇貿易導入準備／參與</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="str">
         <x:v>可重用資產</x:v>
       </x:c>
-      <x:c r="B10" s="48" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B10" s="51" t="str">
+        <x:v>進銷存總圖、八大循環定位圖、訪談前置包、新手顧問導入基礎包</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="22" t="str">
         <x:v>成功標準</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="str">
-        <x:v>待填寫</x:v>
+      <x:c r="B11" s="52" t="str">
+        <x:v>完成3條Odoo端到端流程、2張流程圖、1份建大復盤、1份興宇訪談前置包及至少6筆E2/E3證據候選</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
@@ -4439,219 +4599,387 @@
         <x:v>完成率</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B15" s="27" t="str"/>
-      <x:c r="C15" s="27" t="str"/>
-      <x:c r="D15" s="27" t="str"/>
-      <x:c r="E15" s="27" t="str"/>
-      <x:c r="F15" s="27" t="str"/>
-      <x:c r="G15" s="27" t="str"/>
-      <x:c r="H15" s="27" t="str">
+      <x:c r="B15" s="33" t="str">
+        <x:v>建立導入學習地圖</x:v>
+      </x:c>
+      <x:c r="C15" s="33" t="str">
+        <x:v>盤點專案階段、Odoo模組、進銷存與八大循環關係</x:v>
+      </x:c>
+      <x:c r="D15" s="33" t="str">
+        <x:v>建大與興宇已知情境</x:v>
+      </x:c>
+      <x:c r="E15" s="33" t="str">
+        <x:v>專案生命週期與Odoo模組概覽</x:v>
+      </x:c>
+      <x:c r="F15" s="33" t="str">
+        <x:v>主管／資深顧問</x:v>
+      </x:c>
+      <x:c r="G15" s="33" t="str">
+        <x:v>個人學習地圖</x:v>
+      </x:c>
+      <x:c r="H15" s="33" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I15" s="27" t="str"/>
-      <x:c r="J15" s="54" t="n">
+      <x:c r="I15" s="33" t="str">
+        <x:v>避免只收藏資料</x:v>
+      </x:c>
+      <x:c r="J15" s="57" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B16" s="28" t="str"/>
-      <x:c r="C16" s="28" t="str"/>
-      <x:c r="D16" s="28" t="str"/>
-      <x:c r="E16" s="28" t="str"/>
-      <x:c r="F16" s="28" t="str"/>
-      <x:c r="G16" s="28" t="str"/>
-      <x:c r="H16" s="28" t="str">
+      <x:c r="B16" s="34" t="str">
+        <x:v>完成銷售到收款基本流程</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="str">
+        <x:v>在測試環境走完客戶、報價、訂單、出貨、發票</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="str">
+        <x:v>Odoo測試公司</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="str">
+        <x:v>銷售主資料、單據與狀態</x:v>
+      </x:c>
+      <x:c r="F16" s="34" t="str">
+        <x:v>同事／AI反例檢查</x:v>
+      </x:c>
+      <x:c r="G16" s="34" t="str">
+        <x:v>操作紀錄＋流程圖</x:v>
+      </x:c>
+      <x:c r="H16" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I16" s="28" t="str"/>
-      <x:c r="J16" s="55" t="n">
+      <x:c r="I16" s="34" t="str">
+        <x:v>會計細節先標待確認</x:v>
+      </x:c>
+      <x:c r="J16" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B17" s="28" t="str"/>
-      <x:c r="C17" s="28" t="str"/>
-      <x:c r="D17" s="28" t="str"/>
-      <x:c r="E17" s="28" t="str"/>
-      <x:c r="F17" s="28" t="str"/>
-      <x:c r="G17" s="28" t="str"/>
-      <x:c r="H17" s="28" t="str">
+      <x:c r="B17" s="34" t="str">
+        <x:v>完成採購到付款基本流程</x:v>
+      </x:c>
+      <x:c r="C17" s="34" t="str">
+        <x:v>走完供應商、詢價、採購、收貨、帳單</x:v>
+      </x:c>
+      <x:c r="D17" s="34" t="str">
+        <x:v>Odoo測試公司</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="str">
+        <x:v>採購主資料、單據與狀態</x:v>
+      </x:c>
+      <x:c r="F17" s="34" t="str">
+        <x:v>同事／AI反例檢查</x:v>
+      </x:c>
+      <x:c r="G17" s="34" t="str">
+        <x:v>操作紀錄＋流程圖</x:v>
+      </x:c>
+      <x:c r="H17" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I17" s="28" t="str"/>
-      <x:c r="J17" s="55" t="n">
+      <x:c r="I17" s="34" t="str">
+        <x:v>不要只看操作影片</x:v>
+      </x:c>
+      <x:c r="J17" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B18" s="28" t="str"/>
-      <x:c r="C18" s="28" t="str"/>
-      <x:c r="D18" s="28" t="str"/>
-      <x:c r="E18" s="28" t="str"/>
-      <x:c r="F18" s="28" t="str"/>
-      <x:c r="G18" s="28" t="str"/>
-      <x:c r="H18" s="28" t="str">
+      <x:c r="B18" s="34" t="str">
+        <x:v>完成庫存與主資料基本流程</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="str">
+        <x:v>練習倉庫、位置、調撥、盤點與產品資料</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="str">
+        <x:v>Odoo測試公司</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="str">
+        <x:v>庫存移動與主資料</x:v>
+      </x:c>
+      <x:c r="F18" s="34" t="str">
+        <x:v>資深顧問</x:v>
+      </x:c>
+      <x:c r="G18" s="34" t="str">
+        <x:v>庫存／主資料檢核表</x:v>
+      </x:c>
+      <x:c r="H18" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I18" s="28" t="str"/>
-      <x:c r="J18" s="55" t="n">
+      <x:c r="I18" s="34" t="str">
+        <x:v>保留專案插單緩衝</x:v>
+      </x:c>
+      <x:c r="J18" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="str"/>
-      <x:c r="C19" s="28" t="str"/>
-      <x:c r="D19" s="28" t="str"/>
-      <x:c r="E19" s="28" t="str"/>
-      <x:c r="F19" s="28" t="str"/>
-      <x:c r="G19" s="28" t="str"/>
-      <x:c r="H19" s="28" t="str">
+      <x:c r="B19" s="34" t="str">
+        <x:v>串接進銷存跨模組關係</x:v>
+      </x:c>
+      <x:c r="C19" s="34" t="str">
+        <x:v>找出單據、狀態、資料與異常的前後影響</x:v>
+      </x:c>
+      <x:c r="D19" s="34" t="str">
+        <x:v>建大或測試資料</x:v>
+      </x:c>
+      <x:c r="E19" s="34" t="str">
+        <x:v>端到端流程與例外</x:v>
+      </x:c>
+      <x:c r="F19" s="34" t="str">
+        <x:v>資深顧問</x:v>
+      </x:c>
+      <x:c r="G19" s="34" t="str">
+        <x:v>進銷存端到端總圖</x:v>
+      </x:c>
+      <x:c r="H19" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I19" s="28" t="str"/>
-      <x:c r="J19" s="55" t="n">
+      <x:c r="I19" s="34" t="str">
+        <x:v>圖先求可解釋再求完整</x:v>
+      </x:c>
+      <x:c r="J19" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B20" s="28" t="str"/>
-      <x:c r="C20" s="28" t="str"/>
-      <x:c r="D20" s="28" t="str"/>
-      <x:c r="E20" s="28" t="str"/>
-      <x:c r="F20" s="28" t="str"/>
-      <x:c r="G20" s="28" t="str"/>
-      <x:c r="H20" s="28" t="str">
+      <x:c r="B20" s="34" t="str">
+        <x:v>建立八大循環基礎地圖</x:v>
+      </x:c>
+      <x:c r="C20" s="34" t="str">
+        <x:v>整理目的、常見風險、控制點及Odoo連結</x:v>
+      </x:c>
+      <x:c r="D20" s="34" t="str">
+        <x:v>公司制度範本與案例</x:v>
+      </x:c>
+      <x:c r="E20" s="34" t="str">
+        <x:v>八大循環概覽</x:v>
+      </x:c>
+      <x:c r="F20" s="34" t="str">
+        <x:v>主管／制度資料</x:v>
+      </x:c>
+      <x:c r="G20" s="34" t="str">
+        <x:v>八大循環定位圖</x:v>
+      </x:c>
+      <x:c r="H20" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I20" s="28" t="str"/>
-      <x:c r="J20" s="55" t="n">
+      <x:c r="I20" s="34" t="str">
+        <x:v>本期只建骨架</x:v>
+      </x:c>
+      <x:c r="J20" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B21" s="28" t="str"/>
-      <x:c r="C21" s="28" t="str"/>
-      <x:c r="D21" s="28" t="str"/>
-      <x:c r="E21" s="28" t="str"/>
-      <x:c r="F21" s="28" t="str"/>
-      <x:c r="G21" s="28" t="str"/>
-      <x:c r="H21" s="28" t="str">
+      <x:c r="B21" s="34" t="str">
+        <x:v>完成建大專案復盤</x:v>
+      </x:c>
+      <x:c r="C21" s="34" t="str">
+        <x:v>整理參與工作、困難、判斷、結果與改善</x:v>
+      </x:c>
+      <x:c r="D21" s="34" t="str">
+        <x:v>建大專案去識別化資料</x:v>
+      </x:c>
+      <x:c r="E21" s="34" t="str">
+        <x:v>案例復盤方法</x:v>
+      </x:c>
+      <x:c r="F21" s="34" t="str">
+        <x:v>專案同事</x:v>
+      </x:c>
+      <x:c r="G21" s="34" t="str">
+        <x:v>去識別化案例</x:v>
+      </x:c>
+      <x:c r="H21" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I21" s="28" t="str"/>
-      <x:c r="J21" s="55" t="n">
+      <x:c r="I21" s="34" t="str">
+        <x:v>提交Git前去識別化</x:v>
+      </x:c>
+      <x:c r="J21" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B22" s="28" t="str"/>
-      <x:c r="C22" s="28" t="str"/>
-      <x:c r="D22" s="28" t="str"/>
-      <x:c r="E22" s="28" t="str"/>
-      <x:c r="F22" s="28" t="str"/>
-      <x:c r="G22" s="28" t="str"/>
-      <x:c r="H22" s="28" t="str">
+      <x:c r="B22" s="34" t="str">
+        <x:v>建立需求訪談基本方法</x:v>
+      </x:c>
+      <x:c r="C22" s="34" t="str">
+        <x:v>練習現況、問題、規則、資料、例外與驗收提問</x:v>
+      </x:c>
+      <x:c r="D22" s="34" t="str">
+        <x:v>模擬情境</x:v>
+      </x:c>
+      <x:c r="E22" s="34" t="str">
+        <x:v>訪談結構與追問</x:v>
+      </x:c>
+      <x:c r="F22" s="34" t="str">
+        <x:v>資深顧問／模擬對象</x:v>
+      </x:c>
+      <x:c r="G22" s="34" t="str">
+        <x:v>通用訪談題綱</x:v>
+      </x:c>
+      <x:c r="H22" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I22" s="28" t="str"/>
-      <x:c r="J22" s="55" t="n">
+      <x:c r="I22" s="34" t="str">
+        <x:v>不要把問卷當訪談</x:v>
+      </x:c>
+      <x:c r="J22" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B23" s="28" t="str"/>
-      <x:c r="C23" s="28" t="str"/>
-      <x:c r="D23" s="28" t="str"/>
-      <x:c r="E23" s="28" t="str"/>
-      <x:c r="F23" s="28" t="str"/>
-      <x:c r="G23" s="28" t="str"/>
-      <x:c r="H23" s="28" t="str">
+      <x:c r="B23" s="34" t="str">
+        <x:v>完成興宇貿易訪談前置包</x:v>
+      </x:c>
+      <x:c r="C23" s="34" t="str">
+        <x:v>整理背景、假設、資料、流程與待確認事項</x:v>
+      </x:c>
+      <x:c r="D23" s="34" t="str">
+        <x:v>興宇貿易專案</x:v>
+      </x:c>
+      <x:c r="E23" s="34" t="str">
+        <x:v>貿易業進銷存情境</x:v>
+      </x:c>
+      <x:c r="F23" s="34" t="str">
+        <x:v>專案負責人</x:v>
+      </x:c>
+      <x:c r="G23" s="34" t="str">
+        <x:v>訪談前置包V1</x:v>
+      </x:c>
+      <x:c r="H23" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I23" s="28" t="str"/>
-      <x:c r="J23" s="55" t="n">
+      <x:c r="I23" s="34" t="str">
+        <x:v>資料不足必須標示</x:v>
+      </x:c>
+      <x:c r="J23" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B24" s="28" t="str"/>
-      <x:c r="C24" s="28" t="str"/>
-      <x:c r="D24" s="28" t="str"/>
-      <x:c r="E24" s="28" t="str"/>
-      <x:c r="F24" s="28" t="str"/>
-      <x:c r="G24" s="28" t="str"/>
-      <x:c r="H24" s="28" t="str">
+      <x:c r="B24" s="34" t="str">
+        <x:v>參與或模擬一次訪談</x:v>
+      </x:c>
+      <x:c r="C24" s="34" t="str">
+        <x:v>觀察提問、矛盾、缺口及後續事項</x:v>
+      </x:c>
+      <x:c r="D24" s="34" t="str">
+        <x:v>興宇真實或模擬訪談</x:v>
+      </x:c>
+      <x:c r="E24" s="34" t="str">
+        <x:v>傾聽、記錄與追問</x:v>
+      </x:c>
+      <x:c r="F24" s="34" t="str">
+        <x:v>訪談主持人</x:v>
+      </x:c>
+      <x:c r="G24" s="34" t="str">
+        <x:v>訪談紀錄＋回饋</x:v>
+      </x:c>
+      <x:c r="H24" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I24" s="28" t="str"/>
-      <x:c r="J24" s="55" t="n">
+      <x:c r="I24" s="34" t="str">
+        <x:v>專案未啟動則使用模擬</x:v>
+      </x:c>
+      <x:c r="J24" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B25" s="28" t="str"/>
-      <x:c r="C25" s="28" t="str"/>
-      <x:c r="D25" s="28" t="str"/>
-      <x:c r="E25" s="28" t="str"/>
-      <x:c r="F25" s="28" t="str"/>
-      <x:c r="G25" s="28" t="str"/>
-      <x:c r="H25" s="28" t="str">
+      <x:c r="B25" s="34" t="str">
+        <x:v>整理需求與流程差異</x:v>
+      </x:c>
+      <x:c r="C25" s="34" t="str">
+        <x:v>區分現行、建議、系統、權責與例外</x:v>
+      </x:c>
+      <x:c r="D25" s="34" t="str">
+        <x:v>興宇或去識別化案例</x:v>
+      </x:c>
+      <x:c r="E25" s="34" t="str">
+        <x:v>需求與流程整理</x:v>
+      </x:c>
+      <x:c r="F25" s="34" t="str">
+        <x:v>專案負責人</x:v>
+      </x:c>
+      <x:c r="G25" s="34" t="str">
+        <x:v>需求／流程整理稿</x:v>
+      </x:c>
+      <x:c r="H25" s="34" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I25" s="28" t="str"/>
-      <x:c r="J25" s="55" t="n">
+      <x:c r="I25" s="34" t="str">
+        <x:v>不自行承諾系統方案</x:v>
+      </x:c>
+      <x:c r="J25" s="58" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B26" s="29" t="str"/>
-      <x:c r="C26" s="29" t="str"/>
-      <x:c r="D26" s="29" t="str"/>
-      <x:c r="E26" s="29" t="str"/>
-      <x:c r="F26" s="29" t="str"/>
-      <x:c r="G26" s="29" t="str"/>
-      <x:c r="H26" s="29" t="str">
+      <x:c r="B26" s="35" t="str">
+        <x:v>完成季度考核與基礎包</x:v>
+      </x:c>
+      <x:c r="C26" s="35" t="str">
+        <x:v>依證據校準能力並決定第二期題目</x:v>
+      </x:c>
+      <x:c r="D26" s="35" t="str">
+        <x:v>PGOS季度考核</x:v>
+      </x:c>
+      <x:c r="E26" s="35" t="str">
+        <x:v>證據評量與復盤</x:v>
+      </x:c>
+      <x:c r="F26" s="35" t="str">
+        <x:v>主管／AI教練</x:v>
+      </x:c>
+      <x:c r="G26" s="35" t="str">
+        <x:v>新手顧問導入基礎包V1</x:v>
+      </x:c>
+      <x:c r="H26" s="35" t="str">
         <x:v>未開始</x:v>
       </x:c>
-      <x:c r="I26" s="29" t="str"/>
-      <x:c r="J26" s="56" t="n">
+      <x:c r="I26" s="35" t="str">
+        <x:v>分數不得脫離證據</x:v>
+      </x:c>
+      <x:c r="J26" s="59" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4775,13 +5103,13 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="59"/>
+      <x:c r="A4" s="62"/>
       <x:c r="B4" s="27"/>
       <x:c r="C4" s="27"/>
       <x:c r="D4" s="27"/>
       <x:c r="E4" s="27"/>
       <x:c r="F4" s="27"/>
-      <x:c r="G4" s="62"/>
+      <x:c r="G4" s="65"/>
       <x:c r="H4" s="27"/>
       <x:c r="I4" s="27"/>
       <x:c r="J4" s="27"/>
@@ -4790,13 +5118,13 @@
       <x:c r="M4" s="19"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="60"/>
+      <x:c r="A5" s="63"/>
       <x:c r="B5" s="28"/>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="28"/>
       <x:c r="E5" s="28"/>
       <x:c r="F5" s="28"/>
-      <x:c r="G5" s="63"/>
+      <x:c r="G5" s="66"/>
       <x:c r="H5" s="28"/>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="28"/>
@@ -4805,13 +5133,13 @@
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="60"/>
+      <x:c r="A6" s="63"/>
       <x:c r="B6" s="28"/>
       <x:c r="C6" s="28"/>
       <x:c r="D6" s="28"/>
       <x:c r="E6" s="28"/>
       <x:c r="F6" s="28"/>
-      <x:c r="G6" s="63"/>
+      <x:c r="G6" s="66"/>
       <x:c r="H6" s="28"/>
       <x:c r="I6" s="28"/>
       <x:c r="J6" s="28"/>
@@ -4820,13 +5148,13 @@
       <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="60"/>
+      <x:c r="A7" s="63"/>
       <x:c r="B7" s="28"/>
       <x:c r="C7" s="28"/>
       <x:c r="D7" s="28"/>
       <x:c r="E7" s="28"/>
       <x:c r="F7" s="28"/>
-      <x:c r="G7" s="63"/>
+      <x:c r="G7" s="66"/>
       <x:c r="H7" s="28"/>
       <x:c r="I7" s="28"/>
       <x:c r="J7" s="28"/>
@@ -4835,13 +5163,13 @@
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="60"/>
+      <x:c r="A8" s="63"/>
       <x:c r="B8" s="28"/>
       <x:c r="C8" s="28"/>
       <x:c r="D8" s="28"/>
       <x:c r="E8" s="28"/>
       <x:c r="F8" s="28"/>
-      <x:c r="G8" s="63"/>
+      <x:c r="G8" s="66"/>
       <x:c r="H8" s="28"/>
       <x:c r="I8" s="28"/>
       <x:c r="J8" s="28"/>
@@ -4850,13 +5178,13 @@
       <x:c r="M8" s="21"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="60"/>
+      <x:c r="A9" s="63"/>
       <x:c r="B9" s="28"/>
       <x:c r="C9" s="28"/>
       <x:c r="D9" s="28"/>
       <x:c r="E9" s="28"/>
       <x:c r="F9" s="28"/>
-      <x:c r="G9" s="63"/>
+      <x:c r="G9" s="66"/>
       <x:c r="H9" s="28"/>
       <x:c r="I9" s="28"/>
       <x:c r="J9" s="28"/>
@@ -4865,13 +5193,13 @@
       <x:c r="M9" s="21"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="60"/>
+      <x:c r="A10" s="63"/>
       <x:c r="B10" s="28"/>
       <x:c r="C10" s="28"/>
       <x:c r="D10" s="28"/>
       <x:c r="E10" s="28"/>
       <x:c r="F10" s="28"/>
-      <x:c r="G10" s="63"/>
+      <x:c r="G10" s="66"/>
       <x:c r="H10" s="28"/>
       <x:c r="I10" s="28"/>
       <x:c r="J10" s="28"/>
@@ -4880,13 +5208,13 @@
       <x:c r="M10" s="21"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="60"/>
+      <x:c r="A11" s="63"/>
       <x:c r="B11" s="28"/>
       <x:c r="C11" s="28"/>
       <x:c r="D11" s="28"/>
       <x:c r="E11" s="28"/>
       <x:c r="F11" s="28"/>
-      <x:c r="G11" s="63"/>
+      <x:c r="G11" s="66"/>
       <x:c r="H11" s="28"/>
       <x:c r="I11" s="28"/>
       <x:c r="J11" s="28"/>
@@ -4895,13 +5223,13 @@
       <x:c r="M11" s="21"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="60"/>
+      <x:c r="A12" s="63"/>
       <x:c r="B12" s="28"/>
       <x:c r="C12" s="28"/>
       <x:c r="D12" s="28"/>
       <x:c r="E12" s="28"/>
       <x:c r="F12" s="28"/>
-      <x:c r="G12" s="63"/>
+      <x:c r="G12" s="66"/>
       <x:c r="H12" s="28"/>
       <x:c r="I12" s="28"/>
       <x:c r="J12" s="28"/>
@@ -4910,13 +5238,13 @@
       <x:c r="M12" s="21"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="60"/>
+      <x:c r="A13" s="63"/>
       <x:c r="B13" s="28"/>
       <x:c r="C13" s="28"/>
       <x:c r="D13" s="28"/>
       <x:c r="E13" s="28"/>
       <x:c r="F13" s="28"/>
-      <x:c r="G13" s="63"/>
+      <x:c r="G13" s="66"/>
       <x:c r="H13" s="28"/>
       <x:c r="I13" s="28"/>
       <x:c r="J13" s="28"/>
@@ -4925,13 +5253,13 @@
       <x:c r="M13" s="21"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="60"/>
+      <x:c r="A14" s="63"/>
       <x:c r="B14" s="28"/>
       <x:c r="C14" s="28"/>
       <x:c r="D14" s="28"/>
       <x:c r="E14" s="28"/>
       <x:c r="F14" s="28"/>
-      <x:c r="G14" s="63"/>
+      <x:c r="G14" s="66"/>
       <x:c r="H14" s="28"/>
       <x:c r="I14" s="28"/>
       <x:c r="J14" s="28"/>
@@ -4940,13 +5268,13 @@
       <x:c r="M14" s="21"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="60"/>
+      <x:c r="A15" s="63"/>
       <x:c r="B15" s="28"/>
       <x:c r="C15" s="28"/>
       <x:c r="D15" s="28"/>
       <x:c r="E15" s="28"/>
       <x:c r="F15" s="28"/>
-      <x:c r="G15" s="63"/>
+      <x:c r="G15" s="66"/>
       <x:c r="H15" s="28"/>
       <x:c r="I15" s="28"/>
       <x:c r="J15" s="28"/>
@@ -4955,13 +5283,13 @@
       <x:c r="M15" s="21"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="60"/>
+      <x:c r="A16" s="63"/>
       <x:c r="B16" s="28"/>
       <x:c r="C16" s="28"/>
       <x:c r="D16" s="28"/>
       <x:c r="E16" s="28"/>
       <x:c r="F16" s="28"/>
-      <x:c r="G16" s="63"/>
+      <x:c r="G16" s="66"/>
       <x:c r="H16" s="28"/>
       <x:c r="I16" s="28"/>
       <x:c r="J16" s="28"/>
@@ -4970,13 +5298,13 @@
       <x:c r="M16" s="21"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="60"/>
+      <x:c r="A17" s="63"/>
       <x:c r="B17" s="28"/>
       <x:c r="C17" s="28"/>
       <x:c r="D17" s="28"/>
       <x:c r="E17" s="28"/>
       <x:c r="F17" s="28"/>
-      <x:c r="G17" s="63"/>
+      <x:c r="G17" s="66"/>
       <x:c r="H17" s="28"/>
       <x:c r="I17" s="28"/>
       <x:c r="J17" s="28"/>
@@ -4985,13 +5313,13 @@
       <x:c r="M17" s="21"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="60"/>
+      <x:c r="A18" s="63"/>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
       <x:c r="D18" s="28"/>
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
-      <x:c r="G18" s="63"/>
+      <x:c r="G18" s="66"/>
       <x:c r="H18" s="28"/>
       <x:c r="I18" s="28"/>
       <x:c r="J18" s="28"/>
@@ -5000,13 +5328,13 @@
       <x:c r="M18" s="21"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="60"/>
+      <x:c r="A19" s="63"/>
       <x:c r="B19" s="28"/>
       <x:c r="C19" s="28"/>
       <x:c r="D19" s="28"/>
       <x:c r="E19" s="28"/>
       <x:c r="F19" s="28"/>
-      <x:c r="G19" s="63"/>
+      <x:c r="G19" s="66"/>
       <x:c r="H19" s="28"/>
       <x:c r="I19" s="28"/>
       <x:c r="J19" s="28"/>
@@ -5015,13 +5343,13 @@
       <x:c r="M19" s="21"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="60"/>
+      <x:c r="A20" s="63"/>
       <x:c r="B20" s="28"/>
       <x:c r="C20" s="28"/>
       <x:c r="D20" s="28"/>
       <x:c r="E20" s="28"/>
       <x:c r="F20" s="28"/>
-      <x:c r="G20" s="63"/>
+      <x:c r="G20" s="66"/>
       <x:c r="H20" s="28"/>
       <x:c r="I20" s="28"/>
       <x:c r="J20" s="28"/>
@@ -5030,13 +5358,13 @@
       <x:c r="M20" s="21"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="60"/>
+      <x:c r="A21" s="63"/>
       <x:c r="B21" s="28"/>
       <x:c r="C21" s="28"/>
       <x:c r="D21" s="28"/>
       <x:c r="E21" s="28"/>
       <x:c r="F21" s="28"/>
-      <x:c r="G21" s="63"/>
+      <x:c r="G21" s="66"/>
       <x:c r="H21" s="28"/>
       <x:c r="I21" s="28"/>
       <x:c r="J21" s="28"/>
@@ -5045,13 +5373,13 @@
       <x:c r="M21" s="21"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="60"/>
+      <x:c r="A22" s="63"/>
       <x:c r="B22" s="28"/>
       <x:c r="C22" s="28"/>
       <x:c r="D22" s="28"/>
       <x:c r="E22" s="28"/>
       <x:c r="F22" s="28"/>
-      <x:c r="G22" s="63"/>
+      <x:c r="G22" s="66"/>
       <x:c r="H22" s="28"/>
       <x:c r="I22" s="28"/>
       <x:c r="J22" s="28"/>
@@ -5060,13 +5388,13 @@
       <x:c r="M22" s="21"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="60"/>
+      <x:c r="A23" s="63"/>
       <x:c r="B23" s="28"/>
       <x:c r="C23" s="28"/>
       <x:c r="D23" s="28"/>
       <x:c r="E23" s="28"/>
       <x:c r="F23" s="28"/>
-      <x:c r="G23" s="63"/>
+      <x:c r="G23" s="66"/>
       <x:c r="H23" s="28"/>
       <x:c r="I23" s="28"/>
       <x:c r="J23" s="28"/>
@@ -5075,13 +5403,13 @@
       <x:c r="M23" s="21"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="60"/>
+      <x:c r="A24" s="63"/>
       <x:c r="B24" s="28"/>
       <x:c r="C24" s="28"/>
       <x:c r="D24" s="28"/>
       <x:c r="E24" s="28"/>
       <x:c r="F24" s="28"/>
-      <x:c r="G24" s="63"/>
+      <x:c r="G24" s="66"/>
       <x:c r="H24" s="28"/>
       <x:c r="I24" s="28"/>
       <x:c r="J24" s="28"/>
@@ -5090,13 +5418,13 @@
       <x:c r="M24" s="21"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="60"/>
+      <x:c r="A25" s="63"/>
       <x:c r="B25" s="28"/>
       <x:c r="C25" s="28"/>
       <x:c r="D25" s="28"/>
       <x:c r="E25" s="28"/>
       <x:c r="F25" s="28"/>
-      <x:c r="G25" s="63"/>
+      <x:c r="G25" s="66"/>
       <x:c r="H25" s="28"/>
       <x:c r="I25" s="28"/>
       <x:c r="J25" s="28"/>
@@ -5105,13 +5433,13 @@
       <x:c r="M25" s="21"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="60"/>
+      <x:c r="A26" s="63"/>
       <x:c r="B26" s="28"/>
       <x:c r="C26" s="28"/>
       <x:c r="D26" s="28"/>
       <x:c r="E26" s="28"/>
       <x:c r="F26" s="28"/>
-      <x:c r="G26" s="63"/>
+      <x:c r="G26" s="66"/>
       <x:c r="H26" s="28"/>
       <x:c r="I26" s="28"/>
       <x:c r="J26" s="28"/>
@@ -5120,13 +5448,13 @@
       <x:c r="M26" s="21"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="60"/>
+      <x:c r="A27" s="63"/>
       <x:c r="B27" s="28"/>
       <x:c r="C27" s="28"/>
       <x:c r="D27" s="28"/>
       <x:c r="E27" s="28"/>
       <x:c r="F27" s="28"/>
-      <x:c r="G27" s="63"/>
+      <x:c r="G27" s="66"/>
       <x:c r="H27" s="28"/>
       <x:c r="I27" s="28"/>
       <x:c r="J27" s="28"/>
@@ -5135,13 +5463,13 @@
       <x:c r="M27" s="21"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="60"/>
+      <x:c r="A28" s="63"/>
       <x:c r="B28" s="28"/>
       <x:c r="C28" s="28"/>
       <x:c r="D28" s="28"/>
       <x:c r="E28" s="28"/>
       <x:c r="F28" s="28"/>
-      <x:c r="G28" s="63"/>
+      <x:c r="G28" s="66"/>
       <x:c r="H28" s="28"/>
       <x:c r="I28" s="28"/>
       <x:c r="J28" s="28"/>
@@ -5150,13 +5478,13 @@
       <x:c r="M28" s="21"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="60"/>
+      <x:c r="A29" s="63"/>
       <x:c r="B29" s="28"/>
       <x:c r="C29" s="28"/>
       <x:c r="D29" s="28"/>
       <x:c r="E29" s="28"/>
       <x:c r="F29" s="28"/>
-      <x:c r="G29" s="63"/>
+      <x:c r="G29" s="66"/>
       <x:c r="H29" s="28"/>
       <x:c r="I29" s="28"/>
       <x:c r="J29" s="28"/>
@@ -5165,13 +5493,13 @@
       <x:c r="M29" s="21"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
-      <x:c r="A30" s="60"/>
+      <x:c r="A30" s="63"/>
       <x:c r="B30" s="28"/>
       <x:c r="C30" s="28"/>
       <x:c r="D30" s="28"/>
       <x:c r="E30" s="28"/>
       <x:c r="F30" s="28"/>
-      <x:c r="G30" s="63"/>
+      <x:c r="G30" s="66"/>
       <x:c r="H30" s="28"/>
       <x:c r="I30" s="28"/>
       <x:c r="J30" s="28"/>
@@ -5180,13 +5508,13 @@
       <x:c r="M30" s="21"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
-      <x:c r="A31" s="60"/>
+      <x:c r="A31" s="63"/>
       <x:c r="B31" s="28"/>
       <x:c r="C31" s="28"/>
       <x:c r="D31" s="28"/>
       <x:c r="E31" s="28"/>
       <x:c r="F31" s="28"/>
-      <x:c r="G31" s="63"/>
+      <x:c r="G31" s="66"/>
       <x:c r="H31" s="28"/>
       <x:c r="I31" s="28"/>
       <x:c r="J31" s="28"/>
@@ -5195,13 +5523,13 @@
       <x:c r="M31" s="21"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
-      <x:c r="A32" s="60"/>
+      <x:c r="A32" s="63"/>
       <x:c r="B32" s="28"/>
       <x:c r="C32" s="28"/>
       <x:c r="D32" s="28"/>
       <x:c r="E32" s="28"/>
       <x:c r="F32" s="28"/>
-      <x:c r="G32" s="63"/>
+      <x:c r="G32" s="66"/>
       <x:c r="H32" s="28"/>
       <x:c r="I32" s="28"/>
       <x:c r="J32" s="28"/>
@@ -5210,13 +5538,13 @@
       <x:c r="M32" s="21"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
-      <x:c r="A33" s="60"/>
+      <x:c r="A33" s="63"/>
       <x:c r="B33" s="28"/>
       <x:c r="C33" s="28"/>
       <x:c r="D33" s="28"/>
       <x:c r="E33" s="28"/>
       <x:c r="F33" s="28"/>
-      <x:c r="G33" s="63"/>
+      <x:c r="G33" s="66"/>
       <x:c r="H33" s="28"/>
       <x:c r="I33" s="28"/>
       <x:c r="J33" s="28"/>
@@ -5225,13 +5553,13 @@
       <x:c r="M33" s="21"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
-      <x:c r="A34" s="60"/>
+      <x:c r="A34" s="63"/>
       <x:c r="B34" s="28"/>
       <x:c r="C34" s="28"/>
       <x:c r="D34" s="28"/>
       <x:c r="E34" s="28"/>
       <x:c r="F34" s="28"/>
-      <x:c r="G34" s="63"/>
+      <x:c r="G34" s="66"/>
       <x:c r="H34" s="28"/>
       <x:c r="I34" s="28"/>
       <x:c r="J34" s="28"/>
@@ -5240,13 +5568,13 @@
       <x:c r="M34" s="21"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
-      <x:c r="A35" s="60"/>
+      <x:c r="A35" s="63"/>
       <x:c r="B35" s="28"/>
       <x:c r="C35" s="28"/>
       <x:c r="D35" s="28"/>
       <x:c r="E35" s="28"/>
       <x:c r="F35" s="28"/>
-      <x:c r="G35" s="63"/>
+      <x:c r="G35" s="66"/>
       <x:c r="H35" s="28"/>
       <x:c r="I35" s="28"/>
       <x:c r="J35" s="28"/>
@@ -5255,13 +5583,13 @@
       <x:c r="M35" s="21"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="60"/>
+      <x:c r="A36" s="63"/>
       <x:c r="B36" s="28"/>
       <x:c r="C36" s="28"/>
       <x:c r="D36" s="28"/>
       <x:c r="E36" s="28"/>
       <x:c r="F36" s="28"/>
-      <x:c r="G36" s="63"/>
+      <x:c r="G36" s="66"/>
       <x:c r="H36" s="28"/>
       <x:c r="I36" s="28"/>
       <x:c r="J36" s="28"/>
@@ -5270,13 +5598,13 @@
       <x:c r="M36" s="21"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
-      <x:c r="A37" s="60"/>
+      <x:c r="A37" s="63"/>
       <x:c r="B37" s="28"/>
       <x:c r="C37" s="28"/>
       <x:c r="D37" s="28"/>
       <x:c r="E37" s="28"/>
       <x:c r="F37" s="28"/>
-      <x:c r="G37" s="63"/>
+      <x:c r="G37" s="66"/>
       <x:c r="H37" s="28"/>
       <x:c r="I37" s="28"/>
       <x:c r="J37" s="28"/>
@@ -5285,13 +5613,13 @@
       <x:c r="M37" s="21"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
-      <x:c r="A38" s="60"/>
+      <x:c r="A38" s="63"/>
       <x:c r="B38" s="28"/>
       <x:c r="C38" s="28"/>
       <x:c r="D38" s="28"/>
       <x:c r="E38" s="28"/>
       <x:c r="F38" s="28"/>
-      <x:c r="G38" s="63"/>
+      <x:c r="G38" s="66"/>
       <x:c r="H38" s="28"/>
       <x:c r="I38" s="28"/>
       <x:c r="J38" s="28"/>
@@ -5300,13 +5628,13 @@
       <x:c r="M38" s="21"/>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
-      <x:c r="A39" s="60"/>
+      <x:c r="A39" s="63"/>
       <x:c r="B39" s="28"/>
       <x:c r="C39" s="28"/>
       <x:c r="D39" s="28"/>
       <x:c r="E39" s="28"/>
       <x:c r="F39" s="28"/>
-      <x:c r="G39" s="63"/>
+      <x:c r="G39" s="66"/>
       <x:c r="H39" s="28"/>
       <x:c r="I39" s="28"/>
       <x:c r="J39" s="28"/>
@@ -5315,13 +5643,13 @@
       <x:c r="M39" s="21"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
-      <x:c r="A40" s="60"/>
+      <x:c r="A40" s="63"/>
       <x:c r="B40" s="28"/>
       <x:c r="C40" s="28"/>
       <x:c r="D40" s="28"/>
       <x:c r="E40" s="28"/>
       <x:c r="F40" s="28"/>
-      <x:c r="G40" s="63"/>
+      <x:c r="G40" s="66"/>
       <x:c r="H40" s="28"/>
       <x:c r="I40" s="28"/>
       <x:c r="J40" s="28"/>
@@ -5330,13 +5658,13 @@
       <x:c r="M40" s="21"/>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
-      <x:c r="A41" s="60"/>
+      <x:c r="A41" s="63"/>
       <x:c r="B41" s="28"/>
       <x:c r="C41" s="28"/>
       <x:c r="D41" s="28"/>
       <x:c r="E41" s="28"/>
       <x:c r="F41" s="28"/>
-      <x:c r="G41" s="63"/>
+      <x:c r="G41" s="66"/>
       <x:c r="H41" s="28"/>
       <x:c r="I41" s="28"/>
       <x:c r="J41" s="28"/>
@@ -5345,13 +5673,13 @@
       <x:c r="M41" s="21"/>
     </x:row>
     <x:row r="42" ht="30" customHeight="1">
-      <x:c r="A42" s="60"/>
+      <x:c r="A42" s="63"/>
       <x:c r="B42" s="28"/>
       <x:c r="C42" s="28"/>
       <x:c r="D42" s="28"/>
       <x:c r="E42" s="28"/>
       <x:c r="F42" s="28"/>
-      <x:c r="G42" s="63"/>
+      <x:c r="G42" s="66"/>
       <x:c r="H42" s="28"/>
       <x:c r="I42" s="28"/>
       <x:c r="J42" s="28"/>
@@ -5360,13 +5688,13 @@
       <x:c r="M42" s="21"/>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
-      <x:c r="A43" s="60"/>
+      <x:c r="A43" s="63"/>
       <x:c r="B43" s="28"/>
       <x:c r="C43" s="28"/>
       <x:c r="D43" s="28"/>
       <x:c r="E43" s="28"/>
       <x:c r="F43" s="28"/>
-      <x:c r="G43" s="63"/>
+      <x:c r="G43" s="66"/>
       <x:c r="H43" s="28"/>
       <x:c r="I43" s="28"/>
       <x:c r="J43" s="28"/>
@@ -5375,13 +5703,13 @@
       <x:c r="M43" s="21"/>
     </x:row>
     <x:row r="44" ht="30" customHeight="1">
-      <x:c r="A44" s="60"/>
+      <x:c r="A44" s="63"/>
       <x:c r="B44" s="28"/>
       <x:c r="C44" s="28"/>
       <x:c r="D44" s="28"/>
       <x:c r="E44" s="28"/>
       <x:c r="F44" s="28"/>
-      <x:c r="G44" s="63"/>
+      <x:c r="G44" s="66"/>
       <x:c r="H44" s="28"/>
       <x:c r="I44" s="28"/>
       <x:c r="J44" s="28"/>
@@ -5390,13 +5718,13 @@
       <x:c r="M44" s="21"/>
     </x:row>
     <x:row r="45" ht="30" customHeight="1">
-      <x:c r="A45" s="60"/>
+      <x:c r="A45" s="63"/>
       <x:c r="B45" s="28"/>
       <x:c r="C45" s="28"/>
       <x:c r="D45" s="28"/>
       <x:c r="E45" s="28"/>
       <x:c r="F45" s="28"/>
-      <x:c r="G45" s="63"/>
+      <x:c r="G45" s="66"/>
       <x:c r="H45" s="28"/>
       <x:c r="I45" s="28"/>
       <x:c r="J45" s="28"/>
@@ -5405,13 +5733,13 @@
       <x:c r="M45" s="21"/>
     </x:row>
     <x:row r="46" ht="30" customHeight="1">
-      <x:c r="A46" s="60"/>
+      <x:c r="A46" s="63"/>
       <x:c r="B46" s="28"/>
       <x:c r="C46" s="28"/>
       <x:c r="D46" s="28"/>
       <x:c r="E46" s="28"/>
       <x:c r="F46" s="28"/>
-      <x:c r="G46" s="63"/>
+      <x:c r="G46" s="66"/>
       <x:c r="H46" s="28"/>
       <x:c r="I46" s="28"/>
       <x:c r="J46" s="28"/>
@@ -5420,13 +5748,13 @@
       <x:c r="M46" s="21"/>
     </x:row>
     <x:row r="47" ht="30" customHeight="1">
-      <x:c r="A47" s="60"/>
+      <x:c r="A47" s="63"/>
       <x:c r="B47" s="28"/>
       <x:c r="C47" s="28"/>
       <x:c r="D47" s="28"/>
       <x:c r="E47" s="28"/>
       <x:c r="F47" s="28"/>
-      <x:c r="G47" s="63"/>
+      <x:c r="G47" s="66"/>
       <x:c r="H47" s="28"/>
       <x:c r="I47" s="28"/>
       <x:c r="J47" s="28"/>
@@ -5435,13 +5763,13 @@
       <x:c r="M47" s="21"/>
     </x:row>
     <x:row r="48" ht="30" customHeight="1">
-      <x:c r="A48" s="60"/>
+      <x:c r="A48" s="63"/>
       <x:c r="B48" s="28"/>
       <x:c r="C48" s="28"/>
       <x:c r="D48" s="28"/>
       <x:c r="E48" s="28"/>
       <x:c r="F48" s="28"/>
-      <x:c r="G48" s="63"/>
+      <x:c r="G48" s="66"/>
       <x:c r="H48" s="28"/>
       <x:c r="I48" s="28"/>
       <x:c r="J48" s="28"/>
@@ -5450,13 +5778,13 @@
       <x:c r="M48" s="21"/>
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
-      <x:c r="A49" s="60"/>
+      <x:c r="A49" s="63"/>
       <x:c r="B49" s="28"/>
       <x:c r="C49" s="28"/>
       <x:c r="D49" s="28"/>
       <x:c r="E49" s="28"/>
       <x:c r="F49" s="28"/>
-      <x:c r="G49" s="63"/>
+      <x:c r="G49" s="66"/>
       <x:c r="H49" s="28"/>
       <x:c r="I49" s="28"/>
       <x:c r="J49" s="28"/>
@@ -5465,13 +5793,13 @@
       <x:c r="M49" s="21"/>
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
-      <x:c r="A50" s="60"/>
+      <x:c r="A50" s="63"/>
       <x:c r="B50" s="28"/>
       <x:c r="C50" s="28"/>
       <x:c r="D50" s="28"/>
       <x:c r="E50" s="28"/>
       <x:c r="F50" s="28"/>
-      <x:c r="G50" s="63"/>
+      <x:c r="G50" s="66"/>
       <x:c r="H50" s="28"/>
       <x:c r="I50" s="28"/>
       <x:c r="J50" s="28"/>
@@ -5480,13 +5808,13 @@
       <x:c r="M50" s="21"/>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
-      <x:c r="A51" s="60"/>
+      <x:c r="A51" s="63"/>
       <x:c r="B51" s="28"/>
       <x:c r="C51" s="28"/>
       <x:c r="D51" s="28"/>
       <x:c r="E51" s="28"/>
       <x:c r="F51" s="28"/>
-      <x:c r="G51" s="63"/>
+      <x:c r="G51" s="66"/>
       <x:c r="H51" s="28"/>
       <x:c r="I51" s="28"/>
       <x:c r="J51" s="28"/>
@@ -5495,13 +5823,13 @@
       <x:c r="M51" s="21"/>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
-      <x:c r="A52" s="60"/>
+      <x:c r="A52" s="63"/>
       <x:c r="B52" s="28"/>
       <x:c r="C52" s="28"/>
       <x:c r="D52" s="28"/>
       <x:c r="E52" s="28"/>
       <x:c r="F52" s="28"/>
-      <x:c r="G52" s="63"/>
+      <x:c r="G52" s="66"/>
       <x:c r="H52" s="28"/>
       <x:c r="I52" s="28"/>
       <x:c r="J52" s="28"/>
@@ -5510,13 +5838,13 @@
       <x:c r="M52" s="21"/>
     </x:row>
     <x:row r="53" ht="30" customHeight="1">
-      <x:c r="A53" s="60"/>
+      <x:c r="A53" s="63"/>
       <x:c r="B53" s="28"/>
       <x:c r="C53" s="28"/>
       <x:c r="D53" s="28"/>
       <x:c r="E53" s="28"/>
       <x:c r="F53" s="28"/>
-      <x:c r="G53" s="63"/>
+      <x:c r="G53" s="66"/>
       <x:c r="H53" s="28"/>
       <x:c r="I53" s="28"/>
       <x:c r="J53" s="28"/>
@@ -5525,13 +5853,13 @@
       <x:c r="M53" s="21"/>
     </x:row>
     <x:row r="54" ht="30" customHeight="1">
-      <x:c r="A54" s="60"/>
+      <x:c r="A54" s="63"/>
       <x:c r="B54" s="28"/>
       <x:c r="C54" s="28"/>
       <x:c r="D54" s="28"/>
       <x:c r="E54" s="28"/>
       <x:c r="F54" s="28"/>
-      <x:c r="G54" s="63"/>
+      <x:c r="G54" s="66"/>
       <x:c r="H54" s="28"/>
       <x:c r="I54" s="28"/>
       <x:c r="J54" s="28"/>
@@ -5540,13 +5868,13 @@
       <x:c r="M54" s="21"/>
     </x:row>
     <x:row r="55" ht="30" customHeight="1">
-      <x:c r="A55" s="61"/>
+      <x:c r="A55" s="64"/>
       <x:c r="B55" s="29"/>
       <x:c r="C55" s="29"/>
       <x:c r="D55" s="29"/>
       <x:c r="E55" s="29"/>
       <x:c r="F55" s="29"/>
-      <x:c r="G55" s="64"/>
+      <x:c r="G55" s="67"/>
       <x:c r="H55" s="29"/>
       <x:c r="I55" s="29"/>
       <x:c r="J55" s="29"/>
@@ -5671,7 +5999,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="45" customHeight="1">
-      <x:c r="A4" s="75"/>
+      <x:c r="A4" s="78"/>
       <x:c r="B4" s="33"/>
       <x:c r="C4" s="33"/>
       <x:c r="D4" s="33"/>
@@ -5685,7 +6013,7 @@
       <x:c r="L4" s="30"/>
     </x:row>
     <x:row r="5" ht="45" customHeight="1">
-      <x:c r="A5" s="76"/>
+      <x:c r="A5" s="79"/>
       <x:c r="B5" s="34"/>
       <x:c r="C5" s="34"/>
       <x:c r="D5" s="34"/>
@@ -5699,7 +6027,7 @@
       <x:c r="L5" s="31"/>
     </x:row>
     <x:row r="6" ht="45" customHeight="1">
-      <x:c r="A6" s="76"/>
+      <x:c r="A6" s="79"/>
       <x:c r="B6" s="34"/>
       <x:c r="C6" s="34"/>
       <x:c r="D6" s="34"/>
@@ -5713,7 +6041,7 @@
       <x:c r="L6" s="31"/>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
-      <x:c r="A7" s="76"/>
+      <x:c r="A7" s="79"/>
       <x:c r="B7" s="34"/>
       <x:c r="C7" s="34"/>
       <x:c r="D7" s="34"/>
@@ -5727,7 +6055,7 @@
       <x:c r="L7" s="31"/>
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
-      <x:c r="A8" s="76"/>
+      <x:c r="A8" s="79"/>
       <x:c r="B8" s="34"/>
       <x:c r="C8" s="34"/>
       <x:c r="D8" s="34"/>
@@ -5741,7 +6069,7 @@
       <x:c r="L8" s="31"/>
     </x:row>
     <x:row r="9" ht="45" customHeight="1">
-      <x:c r="A9" s="76"/>
+      <x:c r="A9" s="79"/>
       <x:c r="B9" s="34"/>
       <x:c r="C9" s="34"/>
       <x:c r="D9" s="34"/>
@@ -5755,7 +6083,7 @@
       <x:c r="L9" s="31"/>
     </x:row>
     <x:row r="10" ht="45" customHeight="1">
-      <x:c r="A10" s="76"/>
+      <x:c r="A10" s="79"/>
       <x:c r="B10" s="34"/>
       <x:c r="C10" s="34"/>
       <x:c r="D10" s="34"/>
@@ -5769,7 +6097,7 @@
       <x:c r="L10" s="31"/>
     </x:row>
     <x:row r="11" ht="45" customHeight="1">
-      <x:c r="A11" s="76"/>
+      <x:c r="A11" s="79"/>
       <x:c r="B11" s="34"/>
       <x:c r="C11" s="34"/>
       <x:c r="D11" s="34"/>
@@ -5783,7 +6111,7 @@
       <x:c r="L11" s="31"/>
     </x:row>
     <x:row r="12" ht="45" customHeight="1">
-      <x:c r="A12" s="76"/>
+      <x:c r="A12" s="79"/>
       <x:c r="B12" s="34"/>
       <x:c r="C12" s="34"/>
       <x:c r="D12" s="34"/>
@@ -5797,7 +6125,7 @@
       <x:c r="L12" s="31"/>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
-      <x:c r="A13" s="76"/>
+      <x:c r="A13" s="79"/>
       <x:c r="B13" s="34"/>
       <x:c r="C13" s="34"/>
       <x:c r="D13" s="34"/>
@@ -5811,7 +6139,7 @@
       <x:c r="L13" s="31"/>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
-      <x:c r="A14" s="76"/>
+      <x:c r="A14" s="79"/>
       <x:c r="B14" s="34"/>
       <x:c r="C14" s="34"/>
       <x:c r="D14" s="34"/>
@@ -5825,7 +6153,7 @@
       <x:c r="L14" s="31"/>
     </x:row>
     <x:row r="15" ht="45" customHeight="1">
-      <x:c r="A15" s="76"/>
+      <x:c r="A15" s="79"/>
       <x:c r="B15" s="34"/>
       <x:c r="C15" s="34"/>
       <x:c r="D15" s="34"/>
@@ -5839,7 +6167,7 @@
       <x:c r="L15" s="31"/>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
-      <x:c r="A16" s="76"/>
+      <x:c r="A16" s="79"/>
       <x:c r="B16" s="34"/>
       <x:c r="C16" s="34"/>
       <x:c r="D16" s="34"/>
@@ -5853,7 +6181,7 @@
       <x:c r="L16" s="31"/>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
-      <x:c r="A17" s="76"/>
+      <x:c r="A17" s="79"/>
       <x:c r="B17" s="34"/>
       <x:c r="C17" s="34"/>
       <x:c r="D17" s="34"/>
@@ -5867,7 +6195,7 @@
       <x:c r="L17" s="31"/>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
-      <x:c r="A18" s="76"/>
+      <x:c r="A18" s="79"/>
       <x:c r="B18" s="34"/>
       <x:c r="C18" s="34"/>
       <x:c r="D18" s="34"/>
@@ -5881,7 +6209,7 @@
       <x:c r="L18" s="31"/>
     </x:row>
     <x:row r="19" ht="45" customHeight="1">
-      <x:c r="A19" s="76"/>
+      <x:c r="A19" s="79"/>
       <x:c r="B19" s="34"/>
       <x:c r="C19" s="34"/>
       <x:c r="D19" s="34"/>
@@ -5895,7 +6223,7 @@
       <x:c r="L19" s="31"/>
     </x:row>
     <x:row r="20" ht="45" customHeight="1">
-      <x:c r="A20" s="76"/>
+      <x:c r="A20" s="79"/>
       <x:c r="B20" s="34"/>
       <x:c r="C20" s="34"/>
       <x:c r="D20" s="34"/>
@@ -5909,7 +6237,7 @@
       <x:c r="L20" s="31"/>
     </x:row>
     <x:row r="21" ht="45" customHeight="1">
-      <x:c r="A21" s="76"/>
+      <x:c r="A21" s="79"/>
       <x:c r="B21" s="34"/>
       <x:c r="C21" s="34"/>
       <x:c r="D21" s="34"/>
@@ -5923,7 +6251,7 @@
       <x:c r="L21" s="31"/>
     </x:row>
     <x:row r="22" ht="45" customHeight="1">
-      <x:c r="A22" s="76"/>
+      <x:c r="A22" s="79"/>
       <x:c r="B22" s="34"/>
       <x:c r="C22" s="34"/>
       <x:c r="D22" s="34"/>
@@ -5937,7 +6265,7 @@
       <x:c r="L22" s="31"/>
     </x:row>
     <x:row r="23" ht="45" customHeight="1">
-      <x:c r="A23" s="76"/>
+      <x:c r="A23" s="79"/>
       <x:c r="B23" s="34"/>
       <x:c r="C23" s="34"/>
       <x:c r="D23" s="34"/>
@@ -5951,7 +6279,7 @@
       <x:c r="L23" s="31"/>
     </x:row>
     <x:row r="24" ht="45" customHeight="1">
-      <x:c r="A24" s="76"/>
+      <x:c r="A24" s="79"/>
       <x:c r="B24" s="34"/>
       <x:c r="C24" s="34"/>
       <x:c r="D24" s="34"/>
@@ -5965,7 +6293,7 @@
       <x:c r="L24" s="31"/>
     </x:row>
     <x:row r="25" ht="45" customHeight="1">
-      <x:c r="A25" s="76"/>
+      <x:c r="A25" s="79"/>
       <x:c r="B25" s="34"/>
       <x:c r="C25" s="34"/>
       <x:c r="D25" s="34"/>
@@ -5979,7 +6307,7 @@
       <x:c r="L25" s="31"/>
     </x:row>
     <x:row r="26" ht="45" customHeight="1">
-      <x:c r="A26" s="76"/>
+      <x:c r="A26" s="79"/>
       <x:c r="B26" s="34"/>
       <x:c r="C26" s="34"/>
       <x:c r="D26" s="34"/>
@@ -5993,7 +6321,7 @@
       <x:c r="L26" s="31"/>
     </x:row>
     <x:row r="27" ht="45" customHeight="1">
-      <x:c r="A27" s="76"/>
+      <x:c r="A27" s="79"/>
       <x:c r="B27" s="34"/>
       <x:c r="C27" s="34"/>
       <x:c r="D27" s="34"/>
@@ -6007,7 +6335,7 @@
       <x:c r="L27" s="31"/>
     </x:row>
     <x:row r="28" ht="45" customHeight="1">
-      <x:c r="A28" s="76"/>
+      <x:c r="A28" s="79"/>
       <x:c r="B28" s="34"/>
       <x:c r="C28" s="34"/>
       <x:c r="D28" s="34"/>
@@ -6021,7 +6349,7 @@
       <x:c r="L28" s="31"/>
     </x:row>
     <x:row r="29" ht="45" customHeight="1">
-      <x:c r="A29" s="76"/>
+      <x:c r="A29" s="79"/>
       <x:c r="B29" s="34"/>
       <x:c r="C29" s="34"/>
       <x:c r="D29" s="34"/>
@@ -6035,7 +6363,7 @@
       <x:c r="L29" s="31"/>
     </x:row>
     <x:row r="30" ht="45" customHeight="1">
-      <x:c r="A30" s="76"/>
+      <x:c r="A30" s="79"/>
       <x:c r="B30" s="34"/>
       <x:c r="C30" s="34"/>
       <x:c r="D30" s="34"/>
@@ -6049,7 +6377,7 @@
       <x:c r="L30" s="31"/>
     </x:row>
     <x:row r="31" ht="45" customHeight="1">
-      <x:c r="A31" s="77"/>
+      <x:c r="A31" s="80"/>
       <x:c r="B31" s="35"/>
       <x:c r="C31" s="35"/>
       <x:c r="D31" s="35"/>
@@ -6160,18 +6488,18 @@
       <x:c r="A4" s="18" t="str">
         <x:v>已盤點能力數</x:v>
       </x:c>
-      <x:c r="B4" s="82" t="n">
+      <x:c r="B4" s="85" t="n">
         <x:f>COUNT('能力盤點'!D4:D50)</x:f>
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
         <x:v>思維與決策</x:v>
       </x:c>
-      <x:c r="E4" s="92" t="n">
+      <x:c r="E4" s="95" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D4,'能力盤點'!D4:D50),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F4" s="93" t="n">
+      <x:c r="F4" s="96" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D4,'能力盤點'!E4:E50),0)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -6180,78 +6508,78 @@
       <x:c r="A5" s="20" t="str">
         <x:v>本季優先能力數</x:v>
       </x:c>
-      <x:c r="B5" s="83" t="n">
+      <x:c r="B5" s="86" t="n">
         <x:f>COUNTIF('能力盤點'!I4:I50,"是")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
         <x:v>ERP與流程</x:v>
       </x:c>
-      <x:c r="E5" s="94" t="n">
+      <x:c r="E5" s="97" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D5,'能力盤點'!D4:D50),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="95" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F5" s="98" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D5,'能力盤點'!E4:E50),0)</x:f>
-        <x:v>3</x:v>
+        <x:v>2.75</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="str">
         <x:v>E3/E4證據數</x:v>
       </x:c>
-      <x:c r="B6" s="83" t="n">
+      <x:c r="B6" s="86" t="n">
         <x:f>COUNTIF('證據紀錄'!E4:E53,"E3")+COUNTIF('證據紀錄'!E4:E53,"E4")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>資料與AI</x:v>
       </x:c>
-      <x:c r="E6" s="94" t="n">
+      <x:c r="E6" s="97" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D6,'能力盤點'!D4:D50),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="98" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D6,'能力盤點'!E4:E50),0)</x:f>
-        <x:v>3</x:v>
+        <x:v>2.7142857142857144</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="20" t="str">
         <x:v>候選／執行專案數</x:v>
       </x:c>
-      <x:c r="B7" s="83" t="n">
+      <x:c r="B7" s="86" t="n">
         <x:f>COUNTIF('專案組合'!L4:L23,"候選")+COUNTIF('專案組合'!L4:L23,"本季執行")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>顧問能力</x:v>
       </x:c>
-      <x:c r="E7" s="94" t="n">
+      <x:c r="E7" s="97" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D7,'能力盤點'!D4:D50),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="95" t="n">
+      <x:c r="F7" s="98" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D7,'能力盤點'!E4:E50),0)</x:f>
-        <x:v>3</x:v>
+        <x:v>2.8333333333333335</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="str">
         <x:v>完成專案數</x:v>
       </x:c>
-      <x:c r="B8" s="83" t="n">
+      <x:c r="B8" s="86" t="n">
         <x:f>COUNTIF('專案組合'!L4:L23,"完成")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>軟實力</x:v>
       </x:c>
-      <x:c r="E8" s="94" t="n">
+      <x:c r="E8" s="97" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D8,'能力盤點'!D4:D50),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F8" s="95" t="n">
+      <x:c r="F8" s="98" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D8,'能力盤點'!E4:E50),0)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -6260,18 +6588,18 @@
       <x:c r="A9" s="20" t="str">
         <x:v>累計實際時數</x:v>
       </x:c>
-      <x:c r="B9" s="83" t="n">
+      <x:c r="B9" s="86" t="n">
         <x:f>SUM('每週執行'!D4:D55)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>執行與身心</x:v>
       </x:c>
-      <x:c r="E9" s="94" t="n">
+      <x:c r="E9" s="97" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D9,'能力盤點'!D4:D50),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="98" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D9,'能力盤點'!E4:E50),0)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -6280,20 +6608,20 @@
       <x:c r="A10" s="22" t="str">
         <x:v>累計新增資產</x:v>
       </x:c>
-      <x:c r="B10" s="84" t="n">
+      <x:c r="B10" s="87" t="n">
         <x:f>SUM('每週執行'!I4:I55)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="22" t="str">
         <x:v>職涯與市場</x:v>
       </x:c>
-      <x:c r="E10" s="96" t="n">
+      <x:c r="E10" s="99" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D10,'能力盤點'!D4:D50),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="100" t="n">
         <x:f>IFERROR(AVERAGEIF('能力盤點'!A4:A50,D10,'能力盤點'!E4:E50),0)</x:f>
-        <x:v>3</x:v>
+        <x:v>2.75</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
@@ -6324,7 +6652,7 @@
         <x:f>COUNTIFS('能力盤點'!D4:D50,"&gt;0",'能力盤點'!J4:J50,"待本人盤點")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="59" t="str">
+      <x:c r="D14" s="62" t="str">
         <x:f>IF('每週執行'!A4="","",'每週執行'!A4)</x:f>
       </x:c>
       <x:c r="E14" s="27" t="str">
@@ -6345,7 +6673,7 @@
         <x:f>COUNTIF('證據紀錄'!K4:K53,"否")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="60" t="str">
+      <x:c r="D15" s="63" t="str">
         <x:f>IF('每週執行'!A5="","",'每週執行'!A5)</x:f>
       </x:c>
       <x:c r="E15" s="28" t="str">
@@ -6366,7 +6694,7 @@
         <x:f>MAX(0,COUNTIF('能力盤點'!I4:I50,"是")-3)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="60" t="str">
+      <x:c r="D16" s="63" t="str">
         <x:f>IF('每週執行'!A6="","",'每週執行'!A6)</x:f>
       </x:c>
       <x:c r="E16" s="28" t="str">
@@ -6385,9 +6713,9 @@
       </x:c>
       <x:c r="B17" s="23" t="n">
         <x:f>IF(OR('12週計畫'!B5="",'12週計畫'!B5="待填寫"),1,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="60" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
         <x:f>IF('每週執行'!A7="","",'每週執行'!A7)</x:f>
       </x:c>
       <x:c r="E17" s="28" t="str">
@@ -6401,7 +6729,7 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="D18" s="60" t="str">
+      <x:c r="D18" s="63" t="str">
         <x:f>IF('每週執行'!A8="","",'每週執行'!A8)</x:f>
       </x:c>
       <x:c r="E18" s="28" t="str">
@@ -6415,18 +6743,18 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="58" t="str">
+      <x:c r="A19" s="61" t="str">
         <x:v>提醒：分數是導航工具，不是人格評價。思維與軟實力以真實情境、外部回饋及長期趨勢判定。</x:v>
       </x:c>
-      <x:c r="B19" s="58"/>
-      <x:c r="C19" s="58"/>
-      <x:c r="D19" s="105" t="str">
+      <x:c r="B19" s="61"/>
+      <x:c r="C19" s="61"/>
+      <x:c r="D19" s="108" t="str">
         <x:f>IF('每週執行'!A9="","",'每週執行'!A9)</x:f>
       </x:c>
-      <x:c r="E19" s="106" t="str">
+      <x:c r="E19" s="109" t="str">
         <x:f>IF('每週執行'!A9="","",'每週執行'!D9)</x:f>
       </x:c>
-      <x:c r="F19" s="106" t="str">
+      <x:c r="F19" s="109" t="str">
         <x:f>IF('每週執行'!A9="","",'每週執行'!H9)</x:f>
       </x:c>
       <x:c r="G19" s="21" t="str">
@@ -6434,16 +6762,16 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="58"/>
-      <x:c r="B20" s="58"/>
-      <x:c r="C20" s="58"/>
-      <x:c r="D20" s="105" t="str">
+      <x:c r="A20" s="61"/>
+      <x:c r="B20" s="61"/>
+      <x:c r="C20" s="61"/>
+      <x:c r="D20" s="108" t="str">
         <x:f>IF('每週執行'!A10="","",'每週執行'!A10)</x:f>
       </x:c>
-      <x:c r="E20" s="106" t="str">
+      <x:c r="E20" s="109" t="str">
         <x:f>IF('每週執行'!A10="","",'每週執行'!D10)</x:f>
       </x:c>
-      <x:c r="F20" s="106" t="str">
+      <x:c r="F20" s="109" t="str">
         <x:f>IF('每週執行'!A10="","",'每週執行'!H10)</x:f>
       </x:c>
       <x:c r="G20" s="21" t="str">
@@ -6451,7 +6779,7 @@
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="D21" s="60" t="str">
+      <x:c r="D21" s="63" t="str">
         <x:f>IF('每週執行'!A11="","",'每週執行'!A11)</x:f>
       </x:c>
       <x:c r="E21" s="28" t="str">
@@ -6465,7 +6793,7 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="D22" s="60" t="str">
+      <x:c r="D22" s="63" t="str">
         <x:f>IF('每週執行'!A12="","",'每週執行'!A12)</x:f>
       </x:c>
       <x:c r="E22" s="28" t="str">
@@ -6479,7 +6807,7 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="D23" s="60" t="str">
+      <x:c r="D23" s="63" t="str">
         <x:f>IF('每週執行'!A13="","",'每週執行'!A13)</x:f>
       </x:c>
       <x:c r="E23" s="28" t="str">
@@ -6493,7 +6821,7 @@
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="D24" s="60" t="str">
+      <x:c r="D24" s="63" t="str">
         <x:f>IF('每週執行'!A14="","",'每週執行'!A14)</x:f>
       </x:c>
       <x:c r="E24" s="28" t="str">
@@ -6507,7 +6835,7 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="D25" s="61" t="str">
+      <x:c r="D25" s="64" t="str">
         <x:f>IF('每週執行'!A15="","",'每週執行'!A15)</x:f>
       </x:c>
       <x:c r="E25" s="29" t="str">
@@ -6525,6 +6853,6 @@
     <x:mergeCell ref="A1:N1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R706c00f127384ee5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9116e38108f4639"/>
 </x:worksheet>
 </file>